--- a/artfynd/A 31615-2024 artfynd.xlsx
+++ b/artfynd/A 31615-2024 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031681</v>
+        <v>122031210</v>
       </c>
       <c r="B3" t="n">
         <v>78029</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521777</v>
+        <v>522015</v>
       </c>
       <c r="R3" t="n">
-        <v>6832877</v>
+        <v>6832760</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031210</v>
+        <v>122031796</v>
       </c>
       <c r="B4" t="n">
-        <v>78029</v>
+        <v>78381</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522015</v>
+        <v>521949</v>
       </c>
       <c r="R4" t="n">
-        <v>6832760</v>
+        <v>6832879</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122031796</v>
+        <v>122031681</v>
       </c>
       <c r="B5" t="n">
-        <v>78381</v>
+        <v>78029</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521949</v>
+        <v>521777</v>
       </c>
       <c r="R5" t="n">
-        <v>6832879</v>
+        <v>6832877</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 31615-2024 artfynd.xlsx
+++ b/artfynd/A 31615-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031540</v>
+        <v>122031210</v>
       </c>
       <c r="B2" t="n">
-        <v>78382</v>
+        <v>78030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521949</v>
+        <v>522015</v>
       </c>
       <c r="R2" t="n">
-        <v>6832878</v>
+        <v>6832760</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031210</v>
+        <v>122031540</v>
       </c>
       <c r="B3" t="n">
-        <v>78029</v>
+        <v>78383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522015</v>
+        <v>521949</v>
       </c>
       <c r="R3" t="n">
-        <v>6832760</v>
+        <v>6832878</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031796</v>
+        <v>122031596</v>
       </c>
       <c r="B4" t="n">
-        <v>78381</v>
+        <v>79727</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521949</v>
+        <v>521826</v>
       </c>
       <c r="R4" t="n">
-        <v>6832879</v>
+        <v>6832717</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,7 +1011,7 @@
         <v>122031681</v>
       </c>
       <c r="B5" t="n">
-        <v>78029</v>
+        <v>78030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122031596</v>
+        <v>122031796</v>
       </c>
       <c r="B6" t="n">
-        <v>79726</v>
+        <v>78382</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521826</v>
+        <v>521949</v>
       </c>
       <c r="R6" t="n">
-        <v>6832717</v>
+        <v>6832879</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 31615-2024 artfynd.xlsx
+++ b/artfynd/A 31615-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031210</v>
+        <v>122031540</v>
       </c>
       <c r="B2" t="n">
-        <v>78030</v>
+        <v>78383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522015</v>
+        <v>521949</v>
       </c>
       <c r="R2" t="n">
-        <v>6832760</v>
+        <v>6832878</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031540</v>
+        <v>122031796</v>
       </c>
       <c r="B3" t="n">
-        <v>78383</v>
+        <v>78382</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,7 +833,7 @@
         <v>521949</v>
       </c>
       <c r="R3" t="n">
-        <v>6832878</v>
+        <v>6832879</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031596</v>
+        <v>122031681</v>
       </c>
       <c r="B4" t="n">
-        <v>79727</v>
+        <v>78030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521826</v>
+        <v>521777</v>
       </c>
       <c r="R4" t="n">
-        <v>6832717</v>
+        <v>6832877</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122031681</v>
+        <v>122031596</v>
       </c>
       <c r="B5" t="n">
-        <v>78030</v>
+        <v>79727</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521777</v>
+        <v>521826</v>
       </c>
       <c r="R5" t="n">
-        <v>6832877</v>
+        <v>6832717</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122031796</v>
+        <v>122031210</v>
       </c>
       <c r="B6" t="n">
-        <v>78382</v>
+        <v>78030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521949</v>
+        <v>522015</v>
       </c>
       <c r="R6" t="n">
-        <v>6832879</v>
+        <v>6832760</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 31615-2024 artfynd.xlsx
+++ b/artfynd/A 31615-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031540</v>
+        <v>122031681</v>
       </c>
       <c r="B2" t="n">
-        <v>78383</v>
+        <v>78035</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521949</v>
+        <v>521777</v>
       </c>
       <c r="R2" t="n">
-        <v>6832878</v>
+        <v>6832877</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,7 +789,7 @@
         <v>122031796</v>
       </c>
       <c r="B3" t="n">
-        <v>78382</v>
+        <v>78387</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031681</v>
+        <v>122031540</v>
       </c>
       <c r="B4" t="n">
-        <v>78030</v>
+        <v>78388</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521777</v>
+        <v>521949</v>
       </c>
       <c r="R4" t="n">
-        <v>6832877</v>
+        <v>6832878</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,7 +1011,7 @@
         <v>122031596</v>
       </c>
       <c r="B5" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>122031210</v>
       </c>
       <c r="B6" t="n">
-        <v>78030</v>
+        <v>78035</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 31615-2024 artfynd.xlsx
+++ b/artfynd/A 31615-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031681</v>
+        <v>122031596</v>
       </c>
       <c r="B2" t="n">
-        <v>78035</v>
+        <v>79732</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521777</v>
+        <v>521826</v>
       </c>
       <c r="R2" t="n">
-        <v>6832877</v>
+        <v>6832717</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031796</v>
+        <v>122031540</v>
       </c>
       <c r="B3" t="n">
-        <v>78387</v>
+        <v>78388</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,7 +833,7 @@
         <v>521949</v>
       </c>
       <c r="R3" t="n">
-        <v>6832879</v>
+        <v>6832878</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031540</v>
+        <v>122031796</v>
       </c>
       <c r="B4" t="n">
-        <v>78388</v>
+        <v>78387</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -944,7 +944,7 @@
         <v>521949</v>
       </c>
       <c r="R4" t="n">
-        <v>6832878</v>
+        <v>6832879</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122031596</v>
+        <v>122031210</v>
       </c>
       <c r="B5" t="n">
-        <v>79732</v>
+        <v>78035</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521826</v>
+        <v>522015</v>
       </c>
       <c r="R5" t="n">
-        <v>6832717</v>
+        <v>6832760</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122031210</v>
+        <v>122031681</v>
       </c>
       <c r="B6" t="n">
         <v>78035</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522015</v>
+        <v>521777</v>
       </c>
       <c r="R6" t="n">
-        <v>6832760</v>
+        <v>6832877</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 31615-2024 artfynd.xlsx
+++ b/artfynd/A 31615-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031596</v>
+        <v>122031210</v>
       </c>
       <c r="B2" t="n">
-        <v>79732</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521826</v>
+        <v>522015</v>
       </c>
       <c r="R2" t="n">
-        <v>6832717</v>
+        <v>6832760</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031540</v>
+        <v>122031681</v>
       </c>
       <c r="B3" t="n">
-        <v>78388</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521949</v>
+        <v>521777</v>
       </c>
       <c r="R3" t="n">
-        <v>6832878</v>
+        <v>6832877</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,12 +890,7 @@
         <v>122031796</v>
       </c>
       <c r="B4" t="n">
-        <v>78387</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122031210</v>
+        <v>122031813</v>
       </c>
       <c r="B5" t="n">
-        <v>78035</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522015</v>
+        <v>522089</v>
       </c>
       <c r="R5" t="n">
-        <v>6832760</v>
+        <v>6832743</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122031681</v>
+        <v>122031596</v>
       </c>
       <c r="B6" t="n">
-        <v>78035</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521777</v>
+        <v>521826</v>
       </c>
       <c r="R6" t="n">
-        <v>6832877</v>
+        <v>6832717</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,6 +1202,112 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122031540</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nybyn, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>521949</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6832878</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31615-2024 artfynd.xlsx
+++ b/artfynd/A 31615-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031210</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031681</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031796</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031813</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031596</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,8 +1338,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>